--- a/data/Angemeldete Veranstaltungen.xlsx
+++ b/data/Angemeldete Veranstaltungen.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Lenovo\Dropbox\Pizza &amp; Politik\Aktionswoche\2026\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Lisa-Marie Müller\Dropbox\Pizza &amp; Politik\Aktionswoche\2026\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8756AE50-74FD-4B2A-95E2-D7D72D0DAEAE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{32505ABF-80AC-41BD-B7F1-C4B73883C2B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Tabelle1" sheetId="1" r:id="rId1"/>
@@ -150,10 +150,10 @@
     <t>11.05. um 18:30 Uhr</t>
   </si>
   <si>
-    <t>02.07. um 18:30</t>
-  </si>
-  <si>
     <t>&lt;p&gt;&lt;a href="https://www.instagram.com/larscastellucci/" target="_blank" rel="noopener"&gt;Weitere Infos&lt;/a&gt;</t>
+  </si>
+  <si>
+    <t>02.07. um 18:30 Uhr</t>
   </si>
 </sst>
 </file>
@@ -724,7 +724,7 @@
         <v>40</v>
       </c>
       <c r="G4" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="H4" t="s">
         <v>33</v>
@@ -759,7 +759,7 @@
         <v>39</v>
       </c>
       <c r="G5" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="H5" t="s">
         <v>33</v>
@@ -791,10 +791,10 @@
         <v>37</v>
       </c>
       <c r="F6" t="s">
+        <v>42</v>
+      </c>
+      <c r="G6" t="s">
         <v>41</v>
-      </c>
-      <c r="G6" t="s">
-        <v>42</v>
       </c>
       <c r="H6" t="s">
         <v>33</v>

--- a/data/Angemeldete Veranstaltungen.xlsx
+++ b/data/Angemeldete Veranstaltungen.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Lisa-Marie Müller\Dropbox\Pizza &amp; Politik\Aktionswoche\2026\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{32505ABF-80AC-41BD-B7F1-C4B73883C2B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0C849530-4DA7-4A1F-B83A-6EBBF7BED9C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -141,9 +141,6 @@
     <t>Marktplatz</t>
   </si>
   <si>
-    <t>wird noch bekannt gegeben</t>
-  </si>
-  <si>
     <t>15.06. um 18:00 Uhr</t>
   </si>
   <si>
@@ -154,6 +151,9 @@
   </si>
   <si>
     <t>02.07. um 18:30 Uhr</t>
+  </si>
+  <si>
+    <t>tba</t>
   </si>
 </sst>
 </file>
@@ -721,10 +721,10 @@
         <v>32</v>
       </c>
       <c r="F4" t="s">
+        <v>39</v>
+      </c>
+      <c r="G4" t="s">
         <v>40</v>
-      </c>
-      <c r="G4" t="s">
-        <v>41</v>
       </c>
       <c r="H4" t="s">
         <v>33</v>
@@ -753,13 +753,13 @@
         <v>31</v>
       </c>
       <c r="E5" t="s">
+        <v>42</v>
+      </c>
+      <c r="F5" t="s">
         <v>38</v>
       </c>
-      <c r="F5" t="s">
-        <v>39</v>
-      </c>
       <c r="G5" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="H5" t="s">
         <v>33</v>
@@ -791,10 +791,10 @@
         <v>37</v>
       </c>
       <c r="F6" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="G6" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="H6" t="s">
         <v>33</v>

--- a/data/Angemeldete Veranstaltungen.xlsx
+++ b/data/Angemeldete Veranstaltungen.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Lisa-Marie Müller\Dropbox\Pizza &amp; Politik\Aktionswoche\2026\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0C849530-4DA7-4A1F-B83A-6EBBF7BED9C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8E963D8F-0C79-4A00-80A3-273D91054573}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -153,7 +153,7 @@
     <t>02.07. um 18:30 Uhr</t>
   </si>
   <si>
-    <t>tba</t>
+    <t>wird noch bekanntgegeben</t>
   </si>
 </sst>
 </file>
